--- a/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$333</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1660,12 +1660,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AFI273</t>
+          <t>EU1027</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GFI282</t>
+          <t>EU1033</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AHI23V</t>
+          <t>EU1034</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AHI23W</t>
+          <t>EU1035</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1035</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AHI263</t>
+          <t>EU1036</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1036</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AHI26P</t>
+          <t>EU1037</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1037</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>GEU2CA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AS2004</t>
+          <t>GEU2CB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CB</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AS2005</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AS2006</t>
+          <t>GEU2KW</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KW</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AS3013</t>
+          <t>GEU2KX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1950,19 +1950,19 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KX</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AS3014</t>
+          <t>AFI273</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AS3015</t>
+          <t>FI1040</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2004,19 +2004,19 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1040</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AS3016</t>
+          <t>GFI282</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2031,14 +2031,14 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI282</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>AHI23V</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska de studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AS3018</t>
+          <t>AHI23W</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2085,14 +2085,14 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AS3019</t>
+          <t>AHI263</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2112,14 +2112,14 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>AHI26P</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AS3021</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AS3022</t>
+          <t>AS2004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2004</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AS3023</t>
+          <t>AS2005</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AS3024</t>
+          <t>AS2006</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2006</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AS4005</t>
+          <t>AS3013</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2274,14 +2274,14 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GHI2CK</t>
+          <t>AS3014</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2301,14 +2301,14 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3014</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GHI2FU</t>
+          <t>AS3015</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2328,14 +2328,14 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3015</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GHI2Q6</t>
+          <t>AS3016</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2Q6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande:…</t>
+          <t>Efter avslutad kurs ska de studerande kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>HI1009</t>
+          <t>AS3018</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3018</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>HI2015</t>
+          <t>AS3019</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2436,14 +2436,14 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3019</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>HI3019</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>AS3021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3021</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GKG2CS</t>
+          <t>AS3022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KG1010</t>
+          <t>AS3023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3023</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>AS3024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KG1020</t>
+          <t>AS4005</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4005</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>KG1021</t>
+          <t>GHI2CK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>GHI2FU</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>GHI2Q6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2Q6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KG1027</t>
+          <t>HI1008</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>HI1009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten ha tillägnat sig:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1009</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KG3019</t>
+          <t>HI2015</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2760,19 +2760,19 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2015</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GLP234</t>
+          <t>HI3019</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GLP235</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP235</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>GKG2CS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GLP239</t>
+          <t>KG1010</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1010</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GLP23A</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GLP23B</t>
+          <t>KG1020</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>KG1021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1021</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GLP29T</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GLP29U</t>
+          <t>KG1027</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GLP29V</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten ha tillägnat sig:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GLP29W</t>
+          <t>KG3019</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3019</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GLP29X</t>
+          <t>GLP234</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3111,14 +3111,14 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GLP2BQ</t>
+          <t>GLP235</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3138,14 +3138,14 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP235</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GLP2CX</t>
+          <t>GLP236</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3165,14 +3165,14 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GLP2FH</t>
+          <t>GLP239</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3192,14 +3192,14 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP239</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GLP2FP</t>
+          <t>GLP23A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3219,14 +3219,14 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23A</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GLP2FZ</t>
+          <t>GLP23B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23B</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>GLP29R</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3273,14 +3273,14 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GLP29S</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3300,14 +3300,14 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GLP2MS</t>
+          <t>GLP29T</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29T</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GLP2MU</t>
+          <t>GLP29U</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3354,14 +3354,14 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GLP2NK</t>
+          <t>GLP29V</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GLP2NL</t>
+          <t>GLP29W</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29W</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GLP2NN</t>
+          <t>GLP29X</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3435,14 +3435,14 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29X</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GLP2QC</t>
+          <t>GLP2BQ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3462,14 +3462,14 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GLP2QD</t>
+          <t>GLP2CX</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3489,14 +3489,14 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GLP2QU</t>
+          <t>GLP2FH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3516,14 +3516,14 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FH</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GLP2QX</t>
+          <t>GLP2FP</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3543,14 +3543,14 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FP</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GLP2RK</t>
+          <t>GLP2FZ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2RK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GLP2UG</t>
+          <t>GLP2JZ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3597,14 +3597,14 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GLP2VS</t>
+          <t>GLP2KH</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3624,14 +3624,14 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>GLP2MS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MS</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GLP2WB</t>
+          <t>GLP2MU</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3678,14 +3678,14 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GLP2WC</t>
+          <t>GLP2NK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,19 +3700,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NK</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GLP2WP</t>
+          <t>GLP2NL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GLP32S</t>
+          <t>GLP2NN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>GLP2QC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>LP1052</t>
+          <t>GLP2QD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>LP1053</t>
+          <t>GLP2QU</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3840,14 +3840,14 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>GLP2QX</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>LP1064</t>
+          <t>GLP2RK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3894,14 +3894,14 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2RK</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>LP1065</t>
+          <t>GLP2UG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>GLP2VS</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3948,14 +3948,14 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>LP1072</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3975,14 +3975,14 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>LP1074</t>
+          <t>GLP2WB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4002,14 +4002,14 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>LP1075</t>
+          <t>GLP2WC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4029,14 +4029,14 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>LP1076</t>
+          <t>GLP2WP</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>LP1080</t>
+          <t>GLP32S</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1080</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>LP2009</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4110,14 +4110,14 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>LP2010</t>
+          <t>LP1052</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4137,14 +4137,14 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1052</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>LP1053</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4164,14 +4164,14 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1053</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>LP1054</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GNA2NT</t>
+          <t>LP1064</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1064</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GNA2RY</t>
+          <t>LP1065</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1065</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GNA3B8</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>LP1072</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1072</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>LP1074</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>NA1040</t>
+          <t>LP1075</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1075</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>LP1076</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1076</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GPE2SA</t>
+          <t>LP1080</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1080</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>LP2009</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2009</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>PE1032</t>
+          <t>LP2010</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,24 +4456,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2010</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>PE1053</t>
+          <t>LP2012</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4483,24 +4483,24 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PE1056</t>
+          <t>GNA2NT</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska deltagarna kunna:…</t>
+          <t>Efter genomgången kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PE1059</t>
+          <t>GNA2RY</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1059</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PE1060</t>
+          <t>GNA3B8</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PE2007</t>
+          <t>NA1028</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna:…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PE2016</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>PE3002</t>
+          <t>NA1040</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1040</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>GPE2SA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4731,19 +4731,19 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>PE1032</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>APG282</t>
+          <t>PE1053</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>APG28M</t>
+          <t>PE1056</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska deltagarna kunna:…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>PE1059</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1059</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>PE1060</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>PE2007</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4947,19 +4947,19 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>PE2016</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2016</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GPG2E6</t>
+          <t>PE3002</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>GPA2LN</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5082,14 +5082,14 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Efter avslutad…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>APG282</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5190,14 +5190,14 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5217,14 +5217,14 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>APG28M</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z7</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG2E6</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,24 +5455,24 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5482,24 +5482,24 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5514,19 +5514,19 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5541,19 +5541,19 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ARK262</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5568,19 +5568,19 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GRK2JJ</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GRK2JK</t>
+          <t>GPG2Z7</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>GPG33E</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5779,24 +5779,24 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5806,24 +5806,24 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Efter avslutad delkurs…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5860,19 +5860,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5892,14 +5892,14 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>RK2034</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>RK2038</t>
+          <t>ARK262</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5946,14 +5946,14 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6027,19 +6027,19 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>GRK2JJ</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>RV1002</t>
+          <t>GRK2JK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten…</t>
+          <t>Efter avslutad delkurs…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RK2034</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RK2038</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6319,24 +6319,24 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>RV1044</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Efter fullgjord kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>ASK22G</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>ASK22H</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>ASK22J</t>
+          <t>RV1002</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ASK22K</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs…</t>
+          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>ASK297</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GSK2C9</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter kursen skall studenten:…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>RV1044</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,24 +6724,24 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter fullgjord kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>ASK22G</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6778,19 +6778,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>ASK22H</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6805,19 +6805,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>ASK22J</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6832,19 +6832,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>ASK22K</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6859,19 +6859,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6886,19 +6886,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs…</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6945,14 +6945,14 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>ASK297</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GSK2C9</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6994,19 +6994,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7021,19 +7021,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>SK1054</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7075,19 +7075,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>SK1058</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7134,14 +7134,14 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7156,19 +7156,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7188,14 +7188,14 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7242,14 +7242,14 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7264,19 +7264,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7296,14 +7296,14 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>SK2013</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7323,14 +7323,14 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7345,19 +7345,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7377,19 +7377,19 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7399,24 +7399,24 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>SK1054</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7453,24 +7453,24 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7480,24 +7480,24 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>SO1033</t>
+          <t>SK1058</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7507,24 +7507,24 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>SO1034</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7534,24 +7534,24 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>SO1037</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7561,24 +7561,24 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>SO1047</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7588,24 +7588,24 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7615,24 +7615,24 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7642,24 +7642,24 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7669,24 +7669,24 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>SK2013</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7696,24 +7696,24 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7723,24 +7723,24 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7750,24 +7750,24 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7777,24 +7777,24 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GTR2CT</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7804,24 +7804,24 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7831,24 +7831,24 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7858,24 +7858,24 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7885,24 +7885,24 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>SO1033</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7912,24 +7912,24 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>SO1034</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7939,24 +7939,24 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>SO1037</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7966,24 +7966,24 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7993,24 +7993,24 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>SO1047</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Efter avslutat kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8106,14 +8106,14 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Efter avslutat kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>TR1019</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>GTR2CT</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8263,19 +8263,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8290,19 +8290,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>TR1033</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>TR1035</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8425,19 +8425,19 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>TR1036</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8452,19 +8452,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>TR3009</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8506,24 +8506,24 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutat kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter avslutat kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8668,24 +8668,24 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8754,19 +8754,19 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>AS3007</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>AS3008</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska de studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>AS3010</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8884,24 +8884,24 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>AS3012</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8911,24 +8911,24 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>TR3009</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8938,44 +8938,503 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
+          <t>TR3010</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>AS2001</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>AS2003</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>AS3001</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>AS3003</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>AS3004</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>AS3005</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>AS3006</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>AS3007</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>AS3008</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska de studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>AS3010</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>AS3011</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
           <t>AS4004</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E316" s="2" t="inlineStr">
+      <c r="E333" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E316"/>
+  <autoFilter ref="A1:E333"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -9607,6 +10066,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId628"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId629"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A317" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A320" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A322" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A323" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A324" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A325" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A326" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A327" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A328" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A329" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A330" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A331" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A332" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A333" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId664"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$316</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E333"/>
+  <dimension ref="A1:E316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1660,12 +1660,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EU1027</t>
+          <t>AFI273</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EU1033</t>
+          <t>GFI282</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI282</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EU1034</t>
+          <t>AHI23V</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EU1035</t>
+          <t>AHI23W</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EU1036</t>
+          <t>AHI263</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>EU1037</t>
+          <t>AHI26P</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GEU2CA</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GEU2CB</t>
+          <t>AS2004</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2004</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>AS2005</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GEU2KW</t>
+          <t>AS2006</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2006</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GEU2KX</t>
+          <t>AS3013</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1950,19 +1950,19 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AFI273</t>
+          <t>AS3014</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3014</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FI1040</t>
+          <t>AS3015</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2004,19 +2004,19 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3015</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GFI282</t>
+          <t>AS3016</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2031,14 +2031,14 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AHI23V</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska de studerande kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AHI23W</t>
+          <t>AS3018</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2085,14 +2085,14 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3018</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AHI263</t>
+          <t>AS3019</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2112,14 +2112,14 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3019</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AHI26P</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>AS3021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3021</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AS2004</t>
+          <t>AS3022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AS2005</t>
+          <t>AS3023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3023</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AS2006</t>
+          <t>AS3024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AS3013</t>
+          <t>AS4005</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2274,14 +2274,14 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4005</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AS3014</t>
+          <t>GHI2CK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2301,14 +2301,14 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AS3015</t>
+          <t>GHI2FU</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2328,14 +2328,14 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AS3016</t>
+          <t>GHI2Q6</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2Q6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>HI1008</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska de studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AS3018</t>
+          <t>HI1009</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1009</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AS3019</t>
+          <t>HI2015</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2436,14 +2436,14 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2015</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>HI3019</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AS3021</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AS3022</t>
+          <t>GKG2CS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AS3023</t>
+          <t>KG1010</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1010</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AS3024</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AS4005</t>
+          <t>KG1020</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GHI2CK</t>
+          <t>KG1021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1021</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GHI2FU</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GHI2Q6</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2Q6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>KG1027</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande:…</t>
+          <t>Efter genomgången kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>HI1009</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten ha tillägnat sig:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>HI2015</t>
+          <t>KG3019</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2760,19 +2760,19 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3019</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>HI3019</t>
+          <t>GLP234</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>GLP235</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP235</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GKG2CS</t>
+          <t>GLP236</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>KG1010</t>
+          <t>GLP239</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP239</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>GLP23A</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23A</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KG1020</t>
+          <t>GLP23B</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23B</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>KG1021</t>
+          <t>GLP29R</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>GLP29S</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>GLP29T</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29T</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>KG1027</t>
+          <t>GLP29U</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>GLP29V</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten ha tillägnat sig:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KG3019</t>
+          <t>GLP29W</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29W</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GLP234</t>
+          <t>GLP29X</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3111,14 +3111,14 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29X</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GLP235</t>
+          <t>GLP2BQ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3138,14 +3138,14 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP235</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>GLP2CX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3165,14 +3165,14 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GLP239</t>
+          <t>GLP2FH</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3192,14 +3192,14 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FH</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GLP23A</t>
+          <t>GLP2FP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3219,14 +3219,14 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FP</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GLP23B</t>
+          <t>GLP2FZ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>GLP2JZ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3273,14 +3273,14 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>GLP2KH</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3300,14 +3300,14 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GLP29T</t>
+          <t>GLP2MS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MS</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GLP29U</t>
+          <t>GLP2MU</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3354,14 +3354,14 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GLP29V</t>
+          <t>GLP2NK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NK</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GLP29W</t>
+          <t>GLP2NL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GLP29X</t>
+          <t>GLP2NN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3435,14 +3435,14 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GLP2BQ</t>
+          <t>GLP2QC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3462,14 +3462,14 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GLP2CX</t>
+          <t>GLP2QD</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3489,14 +3489,14 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GLP2FH</t>
+          <t>GLP2QU</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3516,14 +3516,14 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GLP2FP</t>
+          <t>GLP2QX</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3543,14 +3543,14 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GLP2FZ</t>
+          <t>GLP2RK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2RK</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>GLP2UG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3597,14 +3597,14 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GLP2VS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3624,14 +3624,14 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GLP2MS</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GLP2MU</t>
+          <t>GLP2WB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3678,14 +3678,14 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GLP2NK</t>
+          <t>GLP2WC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,19 +3700,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GLP2NL</t>
+          <t>GLP2WP</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GLP2NN</t>
+          <t>GLP32S</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GLP2QC</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GLP2QD</t>
+          <t>LP1052</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1052</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GLP2QU</t>
+          <t>LP1053</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3840,14 +3840,14 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1053</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GLP2QX</t>
+          <t>LP1054</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GLP2RK</t>
+          <t>LP1064</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3894,14 +3894,14 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2RK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1064</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GLP2UG</t>
+          <t>LP1065</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1065</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GLP2VS</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3948,14 +3948,14 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>LP1072</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3975,14 +3975,14 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1072</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GLP2WB</t>
+          <t>LP1074</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4002,14 +4002,14 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GLP2WC</t>
+          <t>LP1075</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4029,14 +4029,14 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1075</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GLP2WP</t>
+          <t>LP1076</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1076</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GLP32S</t>
+          <t>LP1080</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1080</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>LP2009</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4110,14 +4110,14 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2009</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>LP1052</t>
+          <t>LP2010</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4137,14 +4137,14 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2010</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>LP1053</t>
+          <t>LP2012</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4164,14 +4164,14 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>LP1064</t>
+          <t>GNA2NT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>LP1065</t>
+          <t>GNA2RY</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>GNA3B8</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>LP1072</t>
+          <t>NA1028</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna:…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>LP1074</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>LP1075</t>
+          <t>NA1040</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1040</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>LP1076</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>LP1080</t>
+          <t>GPE2SA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1080</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>LP2009</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>LP2010</t>
+          <t>PE1032</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,24 +4456,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>PE1053</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4483,24 +4483,24 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GNA2NT</t>
+          <t>PE1056</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska deltagarna kunna:…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GNA2RY</t>
+          <t>PE1059</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1059</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GNA3B8</t>
+          <t>PE1060</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>PE2007</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>PE2016</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2016</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>NA1040</t>
+          <t>PE3002</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GPE2SA</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4731,19 +4731,19 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PE1032</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PE1053</t>
+          <t>APG282</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>PE1056</t>
+          <t>APG28M</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska deltagarna kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>PE1059</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1059</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>PE1060</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>PE2007</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4947,19 +4947,19 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>PE2016</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>PE3002</t>
+          <t>GPG2E6</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GPA2LN</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5082,14 +5082,14 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>APG282</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5190,14 +5190,14 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5217,14 +5217,14 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>APG28M</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GPG2Z7</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>GPG33E</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPG2E6</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,24 +5455,24 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5482,24 +5482,24 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Efter avslutad…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5514,19 +5514,19 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5541,19 +5541,19 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>ARK262</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5568,19 +5568,19 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>GRK2JJ</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z7</t>
+          <t>GRK2JK</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5779,24 +5779,24 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5806,24 +5806,24 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad delkurs…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5860,19 +5860,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5892,14 +5892,14 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>RK2034</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ARK262</t>
+          <t>RK2038</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5946,14 +5946,14 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6027,19 +6027,19 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GRK2JJ</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GRK2JK</t>
+          <t>RV1002</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Efter avslutad delkurs…</t>
+          <t>Efter genomgången kurs skall studenten…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter kursen skall studenten:…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>RK2034</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RK2038</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6319,24 +6319,24 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>RV1044</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter fullgjord kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>ASK22G</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>ASK22H</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>RV1002</t>
+          <t>ASK22J</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>ASK22K</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
+          <t>Efter avslutad kurs…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>ASK297</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>GSK2C9</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>RV1044</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,24 +6724,24 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Efter fullgjord kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>ASK22G</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6778,19 +6778,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ASK22H</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6805,19 +6805,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ASK22J</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6832,19 +6832,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>ASK22K</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6859,19 +6859,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6886,19 +6886,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6945,14 +6945,14 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ASK297</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSK2C9</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6994,19 +6994,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7021,19 +7021,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>SK1054</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7075,19 +7075,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>SK1058</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7134,14 +7134,14 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7156,19 +7156,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7188,14 +7188,14 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7242,14 +7242,14 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7264,19 +7264,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7296,14 +7296,14 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>SK2013</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7323,14 +7323,14 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7345,19 +7345,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7377,19 +7377,19 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7399,24 +7399,24 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>SK1054</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7453,24 +7453,24 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7480,24 +7480,24 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>SK1058</t>
+          <t>SO1033</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7507,24 +7507,24 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>SO1034</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7534,24 +7534,24 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>SO1037</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7561,24 +7561,24 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>SO1047</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7588,24 +7588,24 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7615,24 +7615,24 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7642,24 +7642,24 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7669,24 +7669,24 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>SK2013</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7696,24 +7696,24 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7723,24 +7723,24 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7750,24 +7750,24 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7777,24 +7777,24 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>GTR2CT</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7804,24 +7804,24 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7831,24 +7831,24 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7858,24 +7858,24 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7885,24 +7885,24 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>SO1033</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7912,24 +7912,24 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>SO1034</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7939,24 +7939,24 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>SO1037</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7966,24 +7966,24 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7993,24 +7993,24 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>SO1047</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutat kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8106,14 +8106,14 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutat kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GTR2CT</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8263,19 +8263,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8290,19 +8290,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8425,19 +8425,19 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8452,19 +8452,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR3009</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8506,24 +8506,24 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Efter avslutat kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Efter avslutat kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>TR1019</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8668,24 +8668,24 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>AS3004</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8754,19 +8754,19 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>AS3007</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>TR1033</t>
+          <t>AS3008</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter avslutad kurs ska de studerande kunna:…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>TR1035</t>
+          <t>AS3010</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>TR1036</t>
+          <t>AS3011</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8884,24 +8884,24 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8911,24 +8911,24 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>TR3009</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8938,24 +8938,24 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>AS4004</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8970,471 +8970,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="inlineStr">
-        <is>
-          <t>AS2001</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E317" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="inlineStr">
-        <is>
-          <t>AS2002</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E318" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>AS2003</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="inlineStr">
-        <is>
-          <t>AS3001</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="inlineStr">
-        <is>
-          <t>AS3002</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>AS3003</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>AS3004</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>AS3005</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="inlineStr">
-        <is>
-          <t>AS3006</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E325" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>AS3007</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E326" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="inlineStr">
-        <is>
-          <t>AS3008</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E327" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2" t="inlineStr">
-        <is>
-          <t>AS3009</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska de studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E328" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="inlineStr">
-        <is>
-          <t>AS3010</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E329" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="2" t="inlineStr">
-        <is>
-          <t>AS3011</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E330" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="inlineStr">
-        <is>
-          <t>AS3012</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E331" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E332" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="inlineStr">
-        <is>
-          <t>AS4004</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E333" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E333"/>
+  <autoFilter ref="A1:E316"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -10066,40 +9607,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId628"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId629"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A317" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A320" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A322" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A323" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A324" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A325" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A326" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A327" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A328" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A329" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A330" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A331" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A332" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A333" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId664"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$329</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4684,12 +4684,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>FPA0002</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4704,19 +4704,19 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>FPA0005</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>APG282</t>
+          <t>FPA0006</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>APG28M</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>FPA2228</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GPG2E6</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska…</t>
+          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5028,14 +5028,14 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5082,14 +5082,14 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Efter avslutad…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>APG282</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5163,14 +5163,14 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5185,19 +5185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>APG28M</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5217,14 +5217,14 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z7</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>GPG2E6</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,24 +5455,24 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5482,24 +5482,24 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5514,19 +5514,19 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5541,19 +5541,19 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ARK262</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5563,24 +5563,24 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GRK2JJ</t>
+          <t>GPG2Z7</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GRK2JK</t>
+          <t>GPG33E</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5779,24 +5779,24 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Efter avslutad delkurs…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5865,14 +5865,14 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5892,14 +5892,14 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>RK2034</t>
+          <t>ARK262</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>RK2038</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5941,19 +5941,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5973,19 +5973,19 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>GRK2JJ</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>GRK2JK</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>RV1002</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
+          <t>Efter avslutad delkurs…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RK2034</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RK2038</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>RV1044</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Efter fullgjord kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>ASK22G</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>ASK22H</t>
+          <t>RV1002</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>ASK22J</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ASK22K</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs…</t>
+          <t>Efter genomgången kurs skall studenten…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>ASK297</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GSK2C9</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter kursen skall studenten:…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>RV1044</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter fullgjord kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>ASK22G</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>ASK22H</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6778,19 +6778,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>ASK22J</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6805,19 +6805,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>ASK22K</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6832,19 +6832,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6864,14 +6864,14 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6886,19 +6886,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs…</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6918,14 +6918,14 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>ASK297</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6945,14 +6945,14 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>GSK2C9</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6999,14 +6999,14 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7021,19 +7021,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>SK1054</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7075,19 +7075,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>SK1058</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7134,14 +7134,14 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7156,19 +7156,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7188,14 +7188,14 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7264,19 +7264,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7296,14 +7296,14 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>SK2013</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7323,14 +7323,14 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7345,19 +7345,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7372,24 +7372,24 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7399,24 +7399,24 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>SK1054</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7431,19 +7431,19 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7453,24 +7453,24 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>SK1058</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7480,24 +7480,24 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>SO1033</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7507,24 +7507,24 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>SO1034</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7534,24 +7534,24 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>SO1037</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7561,24 +7561,24 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>SO1047</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7588,24 +7588,24 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7615,24 +7615,24 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7642,24 +7642,24 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>SK2013</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7669,24 +7669,24 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7696,24 +7696,24 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutade kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7723,24 +7723,24 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7750,24 +7750,24 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7777,24 +7777,24 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GTR2CT</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7804,24 +7804,24 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7831,24 +7831,24 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>SO1033</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7858,24 +7858,24 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>SO1034</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7885,24 +7885,24 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>SO1037</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7912,24 +7912,24 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>SO1047</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7939,19 +7939,19 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7966,19 +7966,19 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7993,19 +7993,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Efter avslutat kurs ska studenten kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8106,14 +8106,14 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Efter avslutat kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>TR1019</t>
+          <t>GTR2CT</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8263,19 +8263,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8290,19 +8290,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>TR1033</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>TR1035</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8425,19 +8425,19 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter avslutat kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>TR1036</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8457,14 +8457,14 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutat kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>TR3009</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8506,24 +8506,24 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8668,24 +8668,24 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8749,24 +8749,24 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>AS3007</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>AS3008</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska de studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>AS3010</t>
+          <t>TR3009</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8857,19 +8857,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8884,19 +8884,19 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>AS3012</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8911,19 +8911,19 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8938,44 +8938,395 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
+          <t>AS3001</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>AS3003</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>AS3004</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>AS3005</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>AS3006</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>AS3007</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>AS3008</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska de studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>AS3010</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>AS3011</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
           <t>AS4004</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E316" s="2" t="inlineStr">
+      <c r="E329" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E316"/>
+  <autoFilter ref="A1:E329"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -9607,6 +9958,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId628"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId629"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A317" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A320" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A322" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A323" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A324" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A325" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A326" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A327" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A328" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A329" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId656"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$321</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E329"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4711,7 +4711,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>FPA0003</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,19 +4726,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>FPA0004</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4753,19 +4753,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>FPA0005</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4780,19 +4780,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>FPA0006</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>FPA0007</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4839,19 +4839,19 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>FPA2227</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4866,19 +4866,19 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>FPA2228</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>FPA222C</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>FPA222D</t>
+          <t>APG282</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>FPA222E</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>FPA222F</t>
+          <t>APG28M</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den forskarstuderande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>FPA222G</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5023,19 +5023,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten:…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5082,14 +5082,14 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>GPG2E6</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>APG282</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5163,14 +5163,14 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5185,19 +5185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>APG28M</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,19 +5212,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GPG2E6</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>GPG2Z7</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Efter avslutad…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>GPG33E</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5509,19 +5509,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z7</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>ARK262</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5779,24 +5779,24 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>GRK2JJ</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>GRK2JK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5865,14 +5865,14 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5892,14 +5892,14 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ARK262</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5941,19 +5941,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad delkurs…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5973,14 +5973,14 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5995,19 +5995,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GRK2JJ</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6027,14 +6027,14 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GRK2JK</t>
+          <t>RK2034</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6054,14 +6054,14 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>RK2038</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6081,14 +6081,14 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6108,19 +6108,19 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Efter avslutad delkurs…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>RV1002</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RK2034</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>RK2038</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,19 +6373,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6400,19 +6400,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter kursen skall studenten:…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>RV1002</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6427,19 +6427,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6454,19 +6454,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>RV1044</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6481,19 +6481,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
+          <t>Efter fullgjord kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>ASK22G</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>ASK22H</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>ASK22J</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>ASK22K</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
+          <t>Efter avslutad kurs…</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>RV1044</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>ASK297</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Efter fullgjord kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>ASK22G</t>
+          <t>GSK2C9</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>ASK22H</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6778,19 +6778,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ASK22J</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6805,19 +6805,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ASK22K</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6832,19 +6832,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6864,14 +6864,14 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6886,19 +6886,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6918,14 +6918,14 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>ASK297</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6945,14 +6945,14 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSK2C9</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6999,14 +6999,14 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7021,19 +7021,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7053,14 +7053,14 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7080,14 +7080,14 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7134,14 +7134,14 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7156,19 +7156,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7183,19 +7183,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>SK1054</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>SK1058</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7269,14 +7269,14 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7291,19 +7291,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7323,14 +7323,14 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7345,19 +7345,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7372,19 +7372,19 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7404,14 +7404,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>SK1054</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7426,19 +7426,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>SK2013</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7458,14 +7458,14 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>SK1058</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7480,19 +7480,19 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7507,24 +7507,24 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7539,19 +7539,19 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7561,24 +7561,24 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7588,24 +7588,24 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7615,24 +7615,24 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>SO1033</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7642,24 +7642,24 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>SK2013</t>
+          <t>SO1034</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7669,24 +7669,24 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>SO1037</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7696,24 +7696,24 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>SO1047</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7723,24 +7723,24 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7750,24 +7750,24 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7777,24 +7777,24 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7804,24 +7804,24 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7831,24 +7831,24 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>SO1033</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7858,24 +7858,24 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>SO1034</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7885,24 +7885,24 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>SO1037</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7912,24 +7912,24 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>SO1047</t>
+          <t>GTR2CT</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7939,19 +7939,19 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7966,19 +7966,19 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7993,19 +7993,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8101,19 +8101,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GTR2CT</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutat kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8263,19 +8263,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter avslutat kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8290,19 +8290,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8425,19 +8425,19 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Efter avslutat kurs ska studenten kunna:…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8457,14 +8457,14 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Efter avslutat kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>TR1019</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8506,19 +8506,19 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8533,19 +8533,19 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8560,19 +8560,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8587,19 +8587,19 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8614,19 +8614,19 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>TR3009</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8668,24 +8668,24 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>TR1033</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8749,24 +8749,24 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>TR1035</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>TR1036</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>AS3004</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>TR3009</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8862,14 +8862,14 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8884,19 +8884,19 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>AS3007</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8911,19 +8911,19 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>AS3008</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8938,19 +8938,19 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8965,19 +8965,19 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska de studerande kunna:…</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3010</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3011</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9019,19 +9019,19 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9051,14 +9051,14 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9073,19 +9073,19 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>AS4004</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9105,228 +9105,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>AS3007</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>AS3008</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>AS3009</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska de studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="inlineStr">
-        <is>
-          <t>AS3010</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E325" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>AS3011</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E326" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="inlineStr">
-        <is>
-          <t>AS3012</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E327" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E328" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="inlineStr">
-        <is>
-          <t>AS4004</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E329" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E329"/>
+  <autoFilter ref="A1:E321"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -9968,22 +9752,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId638"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId639"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A322" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A323" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A324" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A325" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A326" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A327" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A328" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A329" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId656"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$G$321</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:G321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-04-20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2012-02-27</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs skall den studerande visa förmåga att relatera relevant forskning och teorier till egna erfarenhe…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1005</t>
         </is>
@@ -509,15 +531,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-04-20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2012-02-27</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs skall den studerande visa förmåga att relatera relevant forskning och teorier till egna erfarenhe…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1006</t>
         </is>
@@ -536,15 +568,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2010-04-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall den studerande visa förmåga att relatera relevant forskning och teorier till egna erfarenhe…</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1009</t>
         </is>
@@ -563,15 +601,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2011-10-06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Efter kursen ska studenten ha de grundläggande kunskaper och färdigheter som behövs för att kunna reflektera över och ut…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1016</t>
         </is>
@@ -590,15 +634,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2009-11-26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
@@ -617,15 +667,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AU3005</t>
         </is>
@@ -644,15 +700,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2014-03-18</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Efter genomförd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
         </is>
@@ -671,15 +733,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2018-12-10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Efter genomförd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
         </is>
@@ -698,15 +770,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2017-03-22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
         </is>
@@ -725,15 +803,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2017-12-08</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Efter genomförd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2058</t>
         </is>
@@ -752,15 +836,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2018-04-25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ22U</t>
         </is>
@@ -779,15 +869,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ24C</t>
         </is>
@@ -806,15 +902,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2019-03-04</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ27K</t>
         </is>
@@ -833,15 +935,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2019-05-03</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
         </is>
@@ -860,15 +968,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2019-05-03</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
         </is>
@@ -887,15 +1001,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AY</t>
         </is>
@@ -914,15 +1034,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
         </is>
@@ -941,15 +1067,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EB</t>
         </is>
@@ -968,15 +1100,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EC</t>
         </is>
@@ -995,15 +1133,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HC</t>
         </is>
@@ -1022,15 +1166,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HD</t>
         </is>
@@ -1049,15 +1199,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2MT</t>
         </is>
@@ -1076,15 +1232,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Efter genomförd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NH</t>
         </is>
@@ -1103,15 +1265,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NJ</t>
         </is>
@@ -1130,15 +1298,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NM</t>
         </is>
@@ -1157,15 +1331,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
         </is>
@@ -1184,15 +1364,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
         </is>
@@ -1211,15 +1397,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U2</t>
         </is>
@@ -1238,15 +1430,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U3</t>
         </is>
@@ -1265,15 +1463,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U4</t>
         </is>
@@ -1292,15 +1496,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U5</t>
         </is>
@@ -1319,15 +1529,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
@@ -1346,15 +1562,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U7</t>
         </is>
@@ -1373,15 +1595,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U8</t>
         </is>
@@ -1400,15 +1628,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U9</t>
         </is>
@@ -1427,15 +1661,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
@@ -1454,15 +1694,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UD</t>
         </is>
@@ -1481,15 +1727,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UN</t>
         </is>
@@ -1508,15 +1760,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WG</t>
         </is>
@@ -1535,15 +1793,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
@@ -1562,15 +1826,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WJ</t>
         </is>
@@ -1589,15 +1859,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
         </is>
@@ -1616,15 +1892,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XC</t>
         </is>
@@ -1643,15 +1925,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XD</t>
         </is>
@@ -1670,15 +1958,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
@@ -1697,15 +1995,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2019-03-12</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI282</t>
         </is>
@@ -1724,15 +2028,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23V</t>
         </is>
@@ -1751,15 +2061,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI23W</t>
         </is>
@@ -1778,15 +2094,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
         </is>
@@ -1805,15 +2127,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
         </is>
@@ -1832,15 +2160,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
@@ -1859,15 +2193,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2018-02-13</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2004</t>
         </is>
@@ -1886,15 +2226,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2018-02-13</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
@@ -1913,15 +2259,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2018-02-13</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2006</t>
         </is>
@@ -1940,15 +2292,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3013</t>
         </is>
@@ -1967,15 +2325,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3014</t>
         </is>
@@ -1994,15 +2358,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3015</t>
         </is>
@@ -2021,15 +2391,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
         </is>
@@ -2048,15 +2424,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska de studerande kunna:…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
@@ -2075,15 +2457,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3018</t>
         </is>
@@ -2102,15 +2490,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3019</t>
         </is>
@@ -2129,15 +2523,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
@@ -2156,15 +2556,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3021</t>
         </is>
@@ -2183,15 +2593,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
@@ -2210,15 +2630,25 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3023</t>
         </is>
@@ -2237,15 +2667,25 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
         </is>
@@ -2264,15 +2704,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4005</t>
         </is>
@@ -2291,15 +2737,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
         </is>
@@ -2318,15 +2770,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
         </is>
@@ -2345,15 +2803,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2Q6</t>
         </is>
@@ -2372,15 +2836,25 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-11-25</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande:…</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
@@ -2399,15 +2873,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2012-03-12</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1009</t>
         </is>
@@ -2426,15 +2906,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2015</t>
         </is>
@@ -2453,15 +2939,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
@@ -2480,15 +2972,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
@@ -2507,15 +3005,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2020-02-06</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
         </is>
@@ -2534,15 +3038,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2008-01-22</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten:…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1010</t>
         </is>
@@ -2561,15 +3071,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2009-02-24</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
@@ -2588,15 +3104,25 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-02-23</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>2013-12-16</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
         </is>
@@ -2615,15 +3141,25 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-02-23</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>2012-03-14</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1021</t>
         </is>
@@ -2642,15 +3178,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-02-23</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>2012-10-01</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten:…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
@@ -2669,15 +3215,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-04-20</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>2012-10-18</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
@@ -2696,15 +3252,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2010-09-07</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten:…</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1027</t>
         </is>
@@ -2723,15 +3285,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2009-09-02</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten ha tillägnat sig:…</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
@@ -2750,15 +3318,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3019</t>
         </is>
@@ -2777,15 +3351,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>2018-05-21</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
         </is>
@@ -2804,15 +3384,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2018-05-21</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP235</t>
         </is>
@@ -2831,15 +3417,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>2018-05-21</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
@@ -2858,15 +3450,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2018-06-18</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP239</t>
         </is>
@@ -2885,15 +3483,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+          <t>2018-06-18</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23A</t>
         </is>
@@ -2912,15 +3516,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+          <t>2018-06-18</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23B</t>
         </is>
@@ -2939,15 +3549,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
         </is>
@@ -2966,15 +3582,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
         </is>
@@ -2993,15 +3615,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29T</t>
         </is>
@@ -3020,15 +3648,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
         </is>
@@ -3047,15 +3681,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
         </is>
@@ -3074,15 +3714,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29W</t>
         </is>
@@ -3101,15 +3747,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29X</t>
         </is>
@@ -3128,15 +3780,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
         </is>
@@ -3155,15 +3813,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+          <t>2020-01-31</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
         </is>
@@ -3182,15 +3846,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
+          <t>2020-03-10</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FH</t>
         </is>
@@ -3209,15 +3879,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FP</t>
         </is>
@@ -3236,15 +3912,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
         </is>
@@ -3263,15 +3945,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
@@ -3290,15 +3978,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
@@ -3317,15 +4011,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MS</t>
         </is>
@@ -3344,15 +4044,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
         </is>
@@ -3371,15 +4077,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NK</t>
         </is>
@@ -3398,15 +4110,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
         </is>
@@ -3425,15 +4143,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
         </is>
@@ -3452,15 +4176,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
         </is>
@@ -3479,15 +4209,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
         </is>
@@ -3506,15 +4242,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
         </is>
@@ -3533,15 +4275,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
         </is>
@@ -3560,15 +4308,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2RK</t>
         </is>
@@ -3587,15 +4341,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
+          <t>2022-02-18</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
         </is>
@@ -3614,15 +4374,21 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
+          <t>2022-03-09</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
         </is>
@@ -3641,15 +4407,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
+          <t>2022-03-11</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
@@ -3668,15 +4440,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
         </is>
@@ -3695,15 +4473,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
         </is>
@@ -3722,15 +4506,21 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
         </is>
@@ -3749,15 +4539,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
         </is>
@@ -3776,15 +4572,25 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-05-03</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>2018-06-15</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
@@ -3803,15 +4609,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+          <t>2014-09-02</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1052</t>
         </is>
@@ -3830,15 +4642,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+          <t>2014-10-03</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1053</t>
         </is>
@@ -3857,15 +4675,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
@@ -3884,15 +4708,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1064</t>
         </is>
@@ -3911,15 +4741,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1065</t>
         </is>
@@ -3938,15 +4774,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-12-10</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
@@ -3965,15 +4811,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
+          <t>2016-02-19</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1072</t>
         </is>
@@ -3992,15 +4844,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
+          <t>2016-02-19</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
         </is>
@@ -4019,15 +4877,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+          <t>2016-06-09</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1075</t>
         </is>
@@ -4046,15 +4910,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+          <t>2016-06-09</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1076</t>
         </is>
@@ -4073,15 +4943,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+          <t>2016-12-21</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1080</t>
         </is>
@@ -4100,15 +4976,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
+          <t>2016-04-20</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2009</t>
         </is>
@@ -4127,15 +5009,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
+          <t>2016-04-20</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2010</t>
         </is>
@@ -4154,15 +5042,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
@@ -4181,15 +5075,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
@@ -4208,15 +5108,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
         </is>
@@ -4235,15 +5141,21 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
         </is>
@@ -4262,15 +5174,21 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
         </is>
@@ -4289,15 +5207,25 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2009-10-19</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>2013-03-07</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenterna:…</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
@@ -4316,15 +5244,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
+          <t>2014-03-13</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
@@ -4343,15 +5277,21 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
+          <t>2015-03-20</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1040</t>
         </is>
@@ -4370,15 +5310,21 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
@@ -4397,15 +5343,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
         </is>
@@ -4424,15 +5376,25 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2006-11-27</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
@@ -4451,15 +5413,25 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2007-10-22</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
         </is>
@@ -4478,15 +5450,25 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-08-24</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
         </is>
@@ -4505,15 +5487,25 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-04-05</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
@@ -4532,15 +5524,25 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2012-04-05</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska deltagarna kunna:…</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
         </is>
@@ -4559,15 +5561,25 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-08-30</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1059</t>
         </is>
@@ -4586,15 +5598,25 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
         </is>
@@ -4613,15 +5635,25 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2008-04-22</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
         </is>
@@ -4640,15 +5672,25 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-10-07</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2016</t>
         </is>
@@ -4667,15 +5709,25 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2007-03-13</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t>2013-11-20</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
         </is>
@@ -4694,15 +5746,21 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
+          <t>2018-02-15</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
         </is>
@@ -4721,15 +5779,25 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t>2020-12-16</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
@@ -4748,15 +5816,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
+          <t>2019-09-23</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
@@ -4775,15 +5849,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
+          <t>2021-05-04</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
@@ -4802,15 +5882,21 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+          <t>2021-05-04</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
@@ -4829,15 +5915,25 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
@@ -4856,15 +5952,25 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
@@ -4883,15 +5989,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
@@ -4910,15 +6022,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
@@ -4937,15 +6055,21 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
@@ -4964,15 +6088,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
+          <t>2022-11-21</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
@@ -4991,15 +6121,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
@@ -5018,15 +6154,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
@@ -5045,15 +6187,21 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten:…</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
@@ -5072,15 +6220,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
@@ -5099,15 +6253,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
@@ -5126,15 +6286,25 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
@@ -5153,15 +6323,25 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
@@ -5180,15 +6360,25 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t>2021-03-15</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
@@ -5207,15 +6397,21 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
+          <t>2021-12-09</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
@@ -5234,15 +6430,21 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
+          <t>2021-12-09</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
         <is>
           <t>Efter avslutad…</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
@@ -5261,15 +6463,21 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
@@ -5288,15 +6496,21 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
+          <t>2022-03-15</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
@@ -5315,15 +6529,21 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
@@ -5342,15 +6562,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
+          <t>2022-11-21</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
@@ -5369,15 +6595,21 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
@@ -5396,15 +6628,21 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
@@ -5423,15 +6661,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
@@ -5450,15 +6694,21 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
         </is>
@@ -5477,15 +6727,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
@@ -5504,15 +6760,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
@@ -5531,15 +6793,21 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
@@ -5558,15 +6826,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
@@ -5585,15 +6859,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
+          <t>2017-03-09</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
@@ -5612,15 +6892,21 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
@@ -5639,15 +6925,21 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
@@ -5666,15 +6958,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
@@ -5693,15 +6991,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
@@ -5720,15 +7024,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
         <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
@@ -5747,15 +7057,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
@@ -5774,15 +7090,21 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
@@ -5801,15 +7123,21 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
@@ -5828,15 +7156,21 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
@@ -5855,15 +7189,21 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
@@ -5882,15 +7222,21 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
@@ -5909,15 +7255,21 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
@@ -5936,15 +7288,21 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
         <is>
           <t>Efter avslutad delkurs…</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
@@ -5963,15 +7321,21 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
+          <t>2022-01-12</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
@@ -5990,15 +7354,21 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
@@ -6017,15 +7387,21 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
@@ -6044,15 +7420,21 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
@@ -6071,15 +7453,21 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
@@ -6098,15 +7486,21 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
@@ -6125,15 +7519,21 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
@@ -6152,15 +7552,21 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
+          <t>2019-11-28</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
@@ -6179,15 +7585,21 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
@@ -6206,15 +7618,21 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
@@ -6233,15 +7651,21 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
@@ -6260,15 +7684,21 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
@@ -6287,15 +7717,21 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
@@ -6314,15 +7750,21 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
+          <t>2007-04-04</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten…</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
@@ -6341,15 +7783,21 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
+          <t>2007-05-30</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
@@ -6368,15 +7816,21 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
+          <t>2007-10-03</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
@@ -6395,15 +7849,21 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
+          <t>2009-05-13</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
         <is>
           <t>Efter kursen skall studenten:…</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
@@ -6422,15 +7882,21 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
+          <t>2009-06-08</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
@@ -6449,15 +7915,21 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
+          <t>2012-03-08</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
@@ -6476,15 +7948,21 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
+          <t>2012-11-29</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
@@ -6503,15 +7981,21 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
         <is>
           <t>Efter fullgjord kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
@@ -6530,15 +8014,25 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
         </is>
@@ -6557,15 +8051,25 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
@@ -6584,15 +8088,25 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
           <t>Efter…</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
@@ -6611,15 +8125,25 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
@@ -6638,15 +8162,25 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
@@ -6665,15 +8199,25 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs…</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
@@ -6692,15 +8236,21 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
@@ -6719,15 +8269,21 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
         </is>
@@ -6746,15 +8302,25 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
+          <t>2020-03-03</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
@@ -6773,15 +8339,21 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
@@ -6800,15 +8372,21 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
@@ -6827,15 +8405,21 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
@@ -6854,15 +8438,21 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
@@ -6881,15 +8471,21 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
@@ -6908,15 +8504,25 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
@@ -6935,15 +8541,21 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
@@ -6962,15 +8574,21 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
@@ -6989,15 +8607,21 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
@@ -7016,15 +8640,21 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
         <is>
           <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
@@ -7043,15 +8673,21 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
@@ -7070,15 +8706,21 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
+          <t>2021-05-31</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
@@ -7097,15 +8739,21 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
+          <t>2022-02-21</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
@@ -7124,15 +8772,21 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
+          <t>2022-02-21</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
@@ -7151,15 +8805,25 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
+          <t>2015-08-24</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
           <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
@@ -7178,15 +8842,25 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-04-19</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
+          <t>2016-06-28</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
@@ -7205,15 +8879,21 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
+          <t>2015-02-13</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
@@ -7232,15 +8912,21 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
+          <t>2015-02-13</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
@@ -7259,15 +8945,21 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
+          <t>2015-02-13</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
         </is>
@@ -7286,15 +8978,21 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
+          <t>2015-02-13</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
@@ -7313,15 +9011,25 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-04-09</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
@@ -7340,15 +9048,21 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
+          <t>2015-09-03</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
@@ -7367,15 +9081,21 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
+          <t>2015-09-03</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
@@ -7394,15 +9114,21 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
@@ -7421,15 +9147,21 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
+          <t>2015-02-13</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
@@ -7448,15 +9180,21 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
         </is>
@@ -7475,15 +9213,21 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
         <is>
           <t>Efter avslutade kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
@@ -7502,15 +9246,21 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
@@ -7529,15 +9279,21 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
@@ -7556,15 +9312,21 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
+          <t>2007-01-09</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
@@ -7583,15 +9345,25 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-10-19</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
@@ -7610,15 +9382,25 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-03-11</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
+          <t>2013-08-19</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
@@ -7637,15 +9419,21 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
+          <t>2013-10-10</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
         </is>
@@ -7664,15 +9452,21 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
+          <t>2014-02-25</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
@@ -7691,15 +9485,21 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
+          <t>2015-02-09</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
         </is>
@@ -7718,15 +9518,21 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+          <t>2018-03-16</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
@@ -7745,15 +9551,21 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>2020-09-03</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
@@ -7772,15 +9584,21 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
@@ -7799,15 +9617,21 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
+          <t>2018-04-05</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
@@ -7826,15 +9650,21 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
@@ -7853,15 +9683,21 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
         <is>
           <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="G275" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
@@ -7880,15 +9716,21 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
+          <t>2019-04-18</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="G276" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
@@ -7907,15 +9749,21 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
+          <t>2019-05-22</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="G277" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
@@ -7934,15 +9782,21 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
+          <t>2020-02-06</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="G278" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
@@ -7961,15 +9815,21 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
+          <t>2020-02-06</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="G279" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
@@ -7988,15 +9848,21 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="G280" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
@@ -8015,15 +9881,21 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="G281" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
@@ -8042,15 +9914,21 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
+          <t>2020-04-30</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
         <is>
           <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="G282" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
@@ -8069,15 +9947,21 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E283" s="2" t="inlineStr">
+      <c r="G283" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
@@ -8096,15 +9980,21 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="G284" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
@@ -8123,15 +10013,21 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
+      <c r="G285" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
@@ -8150,15 +10046,25 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2008-01-22</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
+          <t>2009-08-26</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="G286" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
@@ -8177,15 +10083,25 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2009-09-02</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
+          <t>2012-03-27</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="G287" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
@@ -8204,15 +10120,25 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
+          <t>2014-04-23</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
           <t>Efter avslutat kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="G288" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
@@ -8231,15 +10157,25 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2013-03-14</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
+          <t>2015-03-09</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E289" s="2" t="inlineStr">
+      <c r="G289" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
@@ -8258,15 +10194,25 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
+          <t>2015-01-28</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
           <t>Efter avslutat kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E290" s="2" t="inlineStr">
+      <c r="G290" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
@@ -8285,15 +10231,21 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
+          <t>2014-06-05</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E291" s="2" t="inlineStr">
+      <c r="G291" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
@@ -8312,15 +10264,21 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
+          <t>2014-08-28</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
-      <c r="E292" s="2" t="inlineStr">
+      <c r="G292" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
@@ -8339,15 +10297,21 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
+          <t>2014-09-18</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
         <is>
           <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
-      <c r="E293" s="2" t="inlineStr">
+      <c r="G293" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
@@ -8366,15 +10330,21 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
+          <t>2015-12-07</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
-      <c r="E294" s="2" t="inlineStr">
+      <c r="G294" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
@@ -8393,15 +10363,21 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
+          <t>2015-12-07</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
-      <c r="E295" s="2" t="inlineStr">
+      <c r="G295" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
@@ -8420,15 +10396,21 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
+          <t>2016-02-17</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
         <is>
           <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
-      <c r="E296" s="2" t="inlineStr">
+      <c r="G296" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
@@ -8447,15 +10429,21 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E297" s="2" t="inlineStr">
+      <c r="G297" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
@@ -8474,15 +10462,21 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
+          <t>2016-03-24</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E298" s="2" t="inlineStr">
+      <c r="G298" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
@@ -8501,15 +10495,21 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
+          <t>2017-03-09</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E299" s="2" t="inlineStr">
+      <c r="G299" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
@@ -8528,15 +10528,21 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
+          <t>2017-03-09</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
-      <c r="E300" s="2" t="inlineStr">
+      <c r="G300" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
@@ -8555,15 +10561,21 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
         <is>
           <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E301" s="2" t="inlineStr">
+      <c r="G301" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
@@ -8582,15 +10594,21 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
+          <t>2018-03-08</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E302" s="2" t="inlineStr">
+      <c r="G302" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
@@ -8609,15 +10627,21 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
+          <t>2012-04-18</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E303" s="2" t="inlineStr">
+      <c r="G303" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
@@ -8636,15 +10660,21 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
+          <t>2014-12-11</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E304" s="2" t="inlineStr">
+      <c r="G304" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
@@ -8663,15 +10693,21 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E305" s="2" t="inlineStr">
+      <c r="G305" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
@@ -8690,15 +10726,21 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E306" s="2" t="inlineStr">
+      <c r="G306" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
@@ -8717,15 +10759,21 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E307" s="2" t="inlineStr">
+      <c r="G307" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
@@ -8744,15 +10792,25 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E308" s="2" t="inlineStr">
+      <c r="G308" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
@@ -8771,15 +10829,25 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E309" s="2" t="inlineStr">
+      <c r="G309" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
@@ -8798,15 +10866,25 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E310" s="2" t="inlineStr">
+      <c r="G310" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
@@ -8825,15 +10903,25 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-06-17</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E311" s="2" t="inlineStr">
+      <c r="G311" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
@@ -8852,15 +10940,21 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E312" s="2" t="inlineStr">
+      <c r="G312" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
@@ -8879,15 +10973,21 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E313" s="2" t="inlineStr">
+      <c r="G313" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
@@ -8906,15 +11006,21 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E314" s="2" t="inlineStr">
+      <c r="G314" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
         </is>
@@ -8933,15 +11039,21 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E315" s="2" t="inlineStr">
+      <c r="G315" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
         </is>
@@ -8960,15 +11072,21 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska de studerande kunna:…</t>
         </is>
       </c>
-      <c r="E316" s="2" t="inlineStr">
+      <c r="G316" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
@@ -8987,15 +11105,21 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E317" s="2" t="inlineStr">
+      <c r="G317" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
         </is>
@@ -9014,15 +11138,21 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E318" s="2" t="inlineStr">
+      <c r="G318" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
         </is>
@@ -9041,15 +11171,21 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E319" s="2" t="inlineStr">
+      <c r="G319" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
@@ -9068,15 +11204,21 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E320" s="2" t="inlineStr">
+      <c r="G320" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
@@ -9095,663 +11237,669 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E321" s="2" t="inlineStr">
+      <c r="G321" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E321"/>
+  <autoFilter ref="A1:G321"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId344"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId352"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId376"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId386"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId388"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId390"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId394"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId396"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId400"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId406"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId412"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId414"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId416"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId418"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId420"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId422"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId424"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId426"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId428"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId430"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId432"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId434"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId436"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId438"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId440"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId442"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId446"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId450"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId452"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId456"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId458"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId460"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId462"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId466"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId468"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId470"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId472"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId474"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId476"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId478"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId480"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId482"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId484"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId486"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId488"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId490"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId492"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId494"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId496"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId498"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId500"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId502"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId504"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId506"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId508"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId510"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId512"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A258" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId514"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId516"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId518"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId520"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId522"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId524"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId526"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId528"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A266" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId530"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A267" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId532"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A268" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId534"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A269" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId536"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A270" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId538"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A271" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId540"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A272" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId542"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A273" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId544"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A274" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId546"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A275" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId548"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A276" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId550"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A277" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId552"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A278" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId554"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A279" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId556"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A280" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId558"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A281" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId560"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A282" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId562"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId564"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A284" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId566"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A285" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId568"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId570"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A287" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId572"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A288" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId574"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A289" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId576"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A290" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId578"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A291" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId580"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A292" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId582"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId584"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId586"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId588"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId590"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId592"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A298" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId594"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A299" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId596"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A300" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId598"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A301" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId600"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A302" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId602"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A303" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId604"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A304" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId606"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A305" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId608"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A306" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId610"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A307" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId612"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A308" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId614"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A309" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId616"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A310" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId618"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A311" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId620"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A312" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId622"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A313" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId624"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A314" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId626"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A315" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId628"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId630"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A317" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId632"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId634"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId636"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A320" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId638"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId640"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$G$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$G$287</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G321"/>
+  <dimension ref="A1:G287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3341,7 +3341,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GLP234</t>
+          <t>GLP29T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2018-05-21</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -3367,14 +3367,14 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29T</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GLP235</t>
+          <t>GLP29U</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2018-05-21</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -3400,14 +3400,14 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP235</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>GLP29V</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2018-05-21</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -3433,14 +3433,14 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GLP239</t>
+          <t>GLP2BQ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -3466,14 +3466,14 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GLP23A</t>
+          <t>GLP2CX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3499,14 +3499,14 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GLP23B</t>
+          <t>GLP2MU</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -3532,14 +3532,14 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP23B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>GLP2NK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3560,19 +3560,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NK</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GLP29S</t>
+          <t>GLP2NL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -3593,19 +3593,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GLP29T</t>
+          <t>GLP2NN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GLP29U</t>
+          <t>GLP2QX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GLP29V</t>
+          <t>GLP2RK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3697,14 +3697,14 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2RK</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GLP29W</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3730,14 +3730,14 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GLP29X</t>
+          <t>GLP2WP</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3763,14 +3763,14 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GLP2BQ</t>
+          <t>GLP32S</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3796,14 +3796,14 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GLP2CX</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3813,10 +3813,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2020-01-31</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>2011-05-03</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2018-06-15</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -3829,14 +3833,14 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GLP2FH</t>
+          <t>LP1052</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3846,7 +3850,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3857,19 +3861,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1052</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GLP2FP</t>
+          <t>LP1053</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3879,7 +3883,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3895,14 +3899,14 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1053</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GLP2FZ</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3912,10 +3916,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>2015-12-10</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -3923,19 +3931,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>LP1074</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3945,7 +3953,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2016-02-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3961,24 +3969,24 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GNA2NT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3989,29 +3997,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GLP2MS</t>
+          <t>GNA2RY</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -4022,29 +4030,29 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GLP2MU</t>
+          <t>GNA3B8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -4055,32 +4063,36 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GLP2NK</t>
+          <t>NA1028</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2013-03-07</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4088,29 +4100,29 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna:…</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GLP2NL</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2014-03-13</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -4121,29 +4133,29 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GLP2NN</t>
+          <t>NA1040</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2015-03-20</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -4154,29 +4166,29 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2NN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1040</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GLP2QC</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2013-02-21</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -4187,29 +4199,29 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GLP2QD</t>
+          <t>GPE2SA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -4220,32 +4232,36 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GLP2QU</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>2006-11-27</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4253,32 +4269,36 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GLP2QX</t>
+          <t>PE1032</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>2007-10-22</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4286,32 +4306,36 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GLP2RK</t>
+          <t>PE1053</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>2011-08-24</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4319,32 +4343,36 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2RK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GLP2UG</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>2012-04-05</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4352,32 +4380,36 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GLP2VS</t>
+          <t>PE1056</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-03-09</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>2012-04-05</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4385,32 +4417,36 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska deltagarna kunna:…</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>PE1059</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>2013-08-30</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4418,32 +4454,36 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1059</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GLP2WB</t>
+          <t>PE1060</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>2013-09-03</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4451,32 +4491,36 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GLP2WC</t>
+          <t>PE2007</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>2008-04-22</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4484,32 +4528,36 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GLP2WP</t>
+          <t>PE2016</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>2010-10-07</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4517,32 +4565,36 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2016</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GLP32S</t>
+          <t>PE3002</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>2007-03-13</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2013-11-20</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4550,36 +4602,32 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP32S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>FPA0002</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2011-05-03</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2018-06-15</t>
-        </is>
-      </c>
+          <t>2018-02-15</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4587,32 +4635,36 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>LP1052</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>2018-05-30</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2020-12-16</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4620,29 +4672,29 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>LP1053</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
+          <t>2019-09-23</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4653,29 +4705,29 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -4686,29 +4738,29 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>LP1064</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -4719,32 +4771,36 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>LP1065</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -4752,34 +4808,34 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2015-12-10</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4789,29 +4845,29 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>LP1072</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2016-02-19</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -4822,29 +4878,29 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>LP1074</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2016-02-19</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -4860,24 +4916,24 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>LP1075</t>
+          <t>APG282</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -4888,29 +4944,29 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>LP1076</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -4921,29 +4977,29 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>LP1080</t>
+          <t>APG28M</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2016-12-21</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -4954,29 +5010,29 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1080</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>LP2009</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -4992,24 +5048,24 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>LP2010</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2016-04-20</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -5020,29 +5076,29 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter godkänd kurs ska studenten:…</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -5053,29 +5109,29 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -5086,32 +5142,36 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GNA2NT</t>
+          <t>GPG2E6</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5119,32 +5179,36 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska…</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GNA2RY</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5152,32 +5216,36 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GNA3B8</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2021-03-15</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5185,36 +5253,32 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2009-10-19</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2013-03-07</t>
-        </is>
-      </c>
+          <t>2021-12-09</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5222,29 +5286,29 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2014-03-13</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -5255,29 +5319,29 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad…</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>NA1040</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2015-03-20</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -5288,29 +5352,29 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2013-02-21</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -5321,29 +5385,29 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GPE2SA</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -5359,31 +5423,27 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2006-11-27</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2013-03-06</t>
-        </is>
-      </c>
+          <t>2022-11-21</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5391,36 +5451,32 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>PE1032</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2007-10-22</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2013-03-06</t>
-        </is>
-      </c>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5428,36 +5484,32 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>PE1053</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2011-08-24</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2013-03-06</t>
-        </is>
-      </c>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5465,36 +5517,32 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2012-04-05</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2013-03-06</t>
-        </is>
-      </c>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5502,36 +5550,32 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PE1056</t>
+          <t>GPG2Z7</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2012-04-05</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2013-03-06</t>
-        </is>
-      </c>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5539,36 +5583,32 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska deltagarna kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PE1059</t>
+          <t>GPG33E</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2013-08-30</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2014-01-24</t>
-        </is>
-      </c>
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5576,36 +5616,32 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1059</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PE1060</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2014-01-24</t>
-        </is>
-      </c>
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5613,36 +5649,32 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PE2007</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2008-04-22</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2013-03-06</t>
-        </is>
-      </c>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5650,36 +5682,32 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PE2016</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2010-10-07</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2013-03-06</t>
-        </is>
-      </c>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5687,36 +5715,32 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>PE3002</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2007-03-13</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2013-11-20</t>
-        </is>
-      </c>
+          <t>2017-03-09</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5724,29 +5748,29 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>FPA0002</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2018-02-15</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -5757,36 +5781,32 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>FPA0007</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2020-12-16</t>
-        </is>
-      </c>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5799,24 +5819,24 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>FPA2227</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2019-09-23</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -5832,24 +5852,24 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>FPA222E</t>
+          <t>ARK262</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -5865,24 +5885,24 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>FPA222G</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -5893,36 +5913,32 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5935,31 +5951,27 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -5967,29 +5979,29 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>GRK2JJ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -6005,24 +6017,24 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>GRK2JK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -6033,29 +6045,29 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>APG282</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -6071,24 +6083,24 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -6099,29 +6111,29 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>APG28M</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -6132,29 +6144,29 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -6165,29 +6177,29 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad delkurs…</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -6198,29 +6210,29 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -6236,24 +6248,24 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -6264,36 +6276,32 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GPG2E6</t>
+          <t>RK2034</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -6301,36 +6309,32 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>RK2038</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -6343,31 +6347,27 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2021-03-15</t>
-        </is>
-      </c>
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -6380,24 +6380,24 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -6408,29 +6408,29 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -6441,29 +6441,29 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Efter avslutad…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -6474,29 +6474,29 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>RV1002</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -6507,29 +6507,29 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -6540,29 +6540,29 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -6573,29 +6573,29 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -6606,29 +6606,29 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2007-04-04</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -6639,29 +6639,29 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten…</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2007-05-30</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -6672,29 +6672,29 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z7</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -6705,29 +6705,29 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2009-05-13</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -6738,29 +6738,29 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter kursen skall studenten:…</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2009-06-08</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -6771,29 +6771,29 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten:…</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2012-03-08</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -6804,29 +6804,29 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>RV1044</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2012-11-29</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -6837,29 +6837,29 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2017-03-09</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -6870,32 +6870,36 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande självständigt kunna:…</t>
+          <t>Efter fullgjord kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>ASK22G</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -6903,32 +6907,36 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>ASK22H</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -6936,32 +6944,36 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>ASK22J</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -6969,32 +6981,36 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter…</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ARK262</t>
+          <t>ASK22K</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -7002,32 +7018,36 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den…</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -7035,32 +7055,36 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -7068,29 +7092,29 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs…</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -7101,29 +7125,29 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GRK2JJ</t>
+          <t>ASK297</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -7139,27 +7163,31 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GRK2JK</t>
+          <t>GSK2C9</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>2019-11-28</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2020-03-03</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -7167,29 +7195,29 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -7205,24 +7233,24 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -7238,24 +7266,24 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -7271,24 +7299,24 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -7299,29 +7327,29 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Efter avslutad delkurs…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -7337,27 +7365,31 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -7370,24 +7402,24 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -7403,24 +7435,24 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>RK2034</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -7436,24 +7468,24 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>RK2038</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -7469,24 +7501,24 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -7497,29 +7529,29 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -7530,29 +7562,29 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -7563,29 +7595,29 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -7596,29 +7628,29 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>RV1002</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -7629,32 +7661,36 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2015-08-24</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -7662,32 +7698,36 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
+          <t>2011-04-19</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2016-06-28</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -7695,29 +7735,29 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>SK1054</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -7728,29 +7768,29 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande ha grundläggande kunskap om:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2007-04-04</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -7761,29 +7801,29 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>SK1058</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2007-05-30</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -7794,29 +7834,29 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -7827,32 +7867,36 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2009-05-13</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -7860,29 +7904,29 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2009-06-08</t>
+          <t>2015-09-03</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -7893,29 +7937,29 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2012-03-08</t>
+          <t>2015-09-03</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -7926,29 +7970,29 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna redogöra för…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>RV1044</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2012-11-29</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -7959,29 +8003,29 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -7992,19 +8036,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Efter fullgjord kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>ASK22G</t>
+          <t>SK2013</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8014,14 +8058,10 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8029,19 +8069,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>ASK22H</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8051,14 +8091,10 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8066,19 +8102,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutade kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>ASK22J</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8088,14 +8124,10 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8103,36 +8135,32 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Efter…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>ASK22K</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8140,36 +8168,32 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
+          <t>2007-01-09</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8177,34 +8201,34 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
+          <t>2010-10-19</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8214,32 +8238,36 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
+          <t>2013-03-11</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2013-08-19</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8247,29 +8275,29 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ASK297</t>
+          <t>SO1033</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2013-10-10</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -8280,36 +8308,32 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GSK2C9</t>
+          <t>SO1034</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2020-03-03</t>
-        </is>
-      </c>
+          <t>2014-02-25</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8317,29 +8341,29 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>SO1037</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2015-02-09</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -8350,29 +8374,29 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>SO1047</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2018-03-16</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -8383,29 +8407,29 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -8416,29 +8440,29 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -8449,29 +8473,29 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2018-04-05</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -8482,36 +8506,32 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2022-01-21</t>
-        </is>
-      </c>
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8519,29 +8539,29 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -8552,29 +8572,29 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2019-04-18</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -8585,29 +8605,29 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -8618,29 +8638,29 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>GTR2CT</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -8651,29 +8671,29 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -8684,29 +8704,29 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -8717,29 +8737,29 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -8750,29 +8770,29 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
+          <t>2020-04-30</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -8783,36 +8803,32 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2015-08-24</t>
-        </is>
-      </c>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8820,36 +8836,32 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Efter genomförd kurs skall studenterna ha förvärvat grundläggande kunskaper om EU:s institutioner och politikområden. Vi…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2011-04-19</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>2016-06-28</t>
-        </is>
-      </c>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8857,29 +8869,29 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SK1054</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2015-02-13</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -8890,32 +8902,36 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2015-02-13</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>2008-01-22</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2009-08-26</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8923,32 +8939,36 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>SK1058</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2015-02-13</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>2009-09-02</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2012-03-27</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8956,32 +8976,36 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2015-02-13</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2014-04-23</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -8989,34 +9013,34 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutat kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
+          <t>2013-03-14</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2015-03-09</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -9026,32 +9050,36 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2015-09-03</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>2014-02-20</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2015-01-28</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -9059,29 +9087,29 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutat kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2015-09-03</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -9092,29 +9120,29 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -9125,29 +9153,29 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2015-02-13</t>
+          <t>2014-09-18</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -9158,29 +9186,29 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>SK2013</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2015-12-07</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -9191,29 +9219,29 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2015-12-07</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -9224,29 +9252,29 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Efter avslutade kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna;…</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2016-02-17</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -9257,29 +9285,29 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutade studier ska studenten kunna;…</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -9290,29 +9318,29 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2007-01-09</t>
+          <t>2016-03-24</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -9323,36 +9351,32 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2010-10-19</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
+          <t>2017-03-09</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -9360,36 +9384,32 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2013-03-11</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>2013-08-19</t>
-        </is>
-      </c>
+          <t>2017-03-09</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -9397,29 +9417,29 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna :…</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>SO1033</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2013-10-10</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -9430,29 +9450,29 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter slutförd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>SO1034</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2014-02-25</t>
+          <t>2018-03-08</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -9463,29 +9483,29 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>SO1037</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2015-02-09</t>
+          <t>2012-04-18</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -9496,29 +9516,29 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>SO1047</t>
+          <t>TR3009</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2018-03-16</t>
+          <t>2014-12-11</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -9529,29 +9549,29 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -9562,29 +9582,29 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -9595,29 +9615,29 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2018-04-05</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -9628,32 +9648,36 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -9661,32 +9685,36 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -9694,32 +9722,36 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2019-04-18</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -9727,32 +9759,36 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>AS3004</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>2015-06-17</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -9760,29 +9796,29 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GTR2CT</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -9793,29 +9829,29 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -9826,29 +9862,29 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>AS3007</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -9859,29 +9895,29 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>AS3008</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -9892,29 +9928,29 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2020-04-30</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -9925,29 +9961,29 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska de studerande kunna:…</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>AS3010</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -9963,24 +9999,24 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>AS3011</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -9996,24 +10032,24 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -10024,36 +10060,32 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2008-01-22</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>2009-08-26</t>
-        </is>
-      </c>
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -10061,36 +10093,32 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall du som student fått grundläggande kunskaper om att arrangera ett evenemang. Det innebär att…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>AS4004</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2009-09-02</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>2012-03-27</t>
-        </is>
-      </c>
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>Avviker från referensformen</t>
@@ -10098,1167 +10126,17 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall de studerande ha förmåga att;…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>TR1013</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>2013-02-01</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>2014-04-23</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Efter avslutat kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G288" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
-        <is>
-          <t>TR1016</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>2013-03-14</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>2015-03-09</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G289" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>TR1018</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>2014-02-20</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>2015-01-28</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Efter avslutat kurs skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G290" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
-        <is>
-          <t>TR1019</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>2014-06-05</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G291" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>TR1024</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>2014-08-28</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
-        </is>
-      </c>
-      <c r="G292" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>TR1025</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>2014-09-18</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
-        </is>
-      </c>
-      <c r="G293" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>2015-12-07</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
-        </is>
-      </c>
-      <c r="G294" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>2015-12-07</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna;…</t>
-        </is>
-      </c>
-      <c r="G295" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>TR1029</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>2016-02-17</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Efter avslutade studier ska studenten kunna;…</t>
-        </is>
-      </c>
-      <c r="G296" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>TR1030</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>2016-03-03</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G297" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>TR1031</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>2016-03-24</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G298" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>TR1033</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>2017-03-09</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G299" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>2017-03-09</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna :…</t>
-        </is>
-      </c>
-      <c r="G300" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>TR1035</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Efter slutförd kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G301" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>TR1036</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>2018-03-08</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G302" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>2012-04-18</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>TR3009</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>2014-12-11</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G304" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>AS2001</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G305" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>AS2002</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G306" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>AS2003</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs skall den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G307" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>AS3001</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G308" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>AS3002</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G309" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>AS3003</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G310" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>AS3004</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>2015-06-17</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="inlineStr">
-        <is>
-          <t>AS3005</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G312" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>AS3006</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>AS3007</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G314" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="inlineStr">
-        <is>
-          <t>AS3008</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G315" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>AS3009</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska de studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G316" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="inlineStr">
-        <is>
-          <t>AS3010</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G317" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="inlineStr">
-        <is>
-          <t>AS3011</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G318" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>AS3012</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G319" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>2016-05-03</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="G320" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="inlineStr">
-        <is>
-          <t>AS4004</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>2016-05-03</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="G321" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G321"/>
+  <autoFilter ref="A1:G287"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -11832,74 +10710,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId570"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A287" r:id="rId571"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A288" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A289" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A290" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A291" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A292" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A298" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A299" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A300" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A301" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A302" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A303" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A304" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A305" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A306" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A307" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A308" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A309" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A310" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A311" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A312" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A313" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A314" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A315" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A317" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A320" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId640"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
